--- a/data/processed/harmonization/Physical__Thermal_conductivity/harmonized.xlsx
+++ b/data/processed/harmonization/Physical__Thermal_conductivity/harmonized.xlsx
@@ -8122,12 +8122,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>CN_MM71:10</t>
+          <t>CN_MM71:CPIT1:10</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Site:depth</t>
+          <t>Site:Samping_site:depth</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -8157,7 +8157,7 @@
       <c r="K171" s="2" t="inlineStr"/>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth; id not unique: 2 rows share an id</t>
+          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>CN_MM71:18</t>
+          <t>CN_MM71:CPIT1:18</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Site:depth</t>
+          <t>Site:Samping_site:depth</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -8209,7 +8209,7 @@
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth; id not unique: 2 rows share an id</t>
+          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth</t>
         </is>
       </c>
     </row>
@@ -8226,12 +8226,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>CN_MM71:30</t>
+          <t>CN_MM71:CPIT1:30</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Site:depth</t>
+          <t>Site:Samping_site:depth</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth; id not unique: 2 rows share an id</t>
+          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth</t>
         </is>
       </c>
     </row>
@@ -8278,12 +8278,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>CN_MM71:48</t>
+          <t>CN_MM71:CPIT1:48</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Site:depth</t>
+          <t>Site:Samping_site:depth</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -8313,7 +8313,7 @@
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth; id not unique: 2 rows share an id</t>
+          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth</t>
         </is>
       </c>
     </row>
@@ -8330,12 +8330,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>CN_MM71:5</t>
+          <t>CN_MM71:CPIT3:5</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Site:depth</t>
+          <t>Site:Samping_site:depth</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -8365,7 +8365,7 @@
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth; id not unique: 2 rows share an id</t>
+          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>CN_MM71:20</t>
+          <t>CN_MM71:CPIT3:20</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Site:depth</t>
+          <t>Site:Samping_site:depth</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -8417,7 +8417,7 @@
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth; id not unique: 2 rows share an id</t>
+          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth</t>
         </is>
       </c>
     </row>
@@ -8434,12 +8434,12 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>CN_MM71:40</t>
+          <t>CN_MM71:CPIT3:40</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Site:depth</t>
+          <t>Site:Samping_site:depth</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -8469,7 +8469,7 @@
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth; id not unique: 2 rows share an id</t>
+          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth</t>
         </is>
       </c>
     </row>
@@ -8486,12 +8486,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>CN_MM71:15</t>
+          <t>CN_MM71:CPIT4:15</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Site:depth</t>
+          <t>Site:Samping_site:depth</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -8521,7 +8521,7 @@
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth; id not unique: 2 rows share an id</t>
+          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth</t>
         </is>
       </c>
     </row>
@@ -8538,12 +8538,12 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>CN_MM71:40</t>
+          <t>CN_MM71:CPIT4:40</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Site:depth</t>
+          <t>Site:Samping_site:depth</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -8573,7 +8573,7 @@
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth; id not unique: 2 rows share an id</t>
+          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>CN_MM71:56</t>
+          <t>CN_MM71:CPIT4:56</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Site:depth</t>
+          <t>Site:Samping_site:depth</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -8625,7 +8625,7 @@
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth; id not unique: 2 rows share an id</t>
+          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth</t>
         </is>
       </c>
     </row>
@@ -8642,12 +8642,12 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>CN_MM71:65</t>
+          <t>CN_MM71:CPIT4:65</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Site:depth</t>
+          <t>Site:Samping_site:depth</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -8677,7 +8677,7 @@
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth; id not unique: 2 rows share an id</t>
+          <t>lat/long source: doi:10.5440/1417652:CN_MM71_Field_Thermal_Measurements_2016.csv (per-sample columns local_latitude, local_longitude); source column thermal_conductivity_mean (W m^-1 K^-1, unit from units row); depth from sample_depth</t>
         </is>
       </c>
     </row>
